--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/11_17_03_2.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/11_17_03_2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D34349D-0651-134E-97FD-5E6EACF0E0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,19 @@
     <definedName name="MethodPointer1">1827093696</definedName>
     <definedName name="MethodPointer2">594</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -289,7 +307,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -507,38 +525,58 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="zh-CN"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:xVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$Q$25:$Q$28</c:f>
+              <c:f>'板 1 - Sheet1'!$Q$25:$Q$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1.5</c:v>
                 </c:pt>
@@ -551,15 +589,21 @@
                 <c:pt idx="3">
                   <c:v>0.25</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$R$25:$R$28</c:f>
+              <c:f>'板 1 - Sheet1'!$R$25:$R$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0.10300000000000001</c:v>
                 </c:pt>
@@ -572,11 +616,30 @@
                 <c:pt idx="3">
                   <c:v>6.25E-2</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.5999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.7499999999999996E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D1A-1642-963D-8FB856715FC1}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="58544512"/>
         <c:axId val="58542720"/>
       </c:scatterChart>
@@ -585,8 +648,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="58542720"/>
         <c:crosses val="autoZero"/>
@@ -597,9 +663,12 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="58544512"/>
         <c:crosses val="autoZero"/>
@@ -608,9 +677,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -637,7 +708,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -656,7 +733,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -698,7 +775,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -730,9 +807,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -764,6 +859,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -939,15 +1052,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:R32"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -955,7 +1068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -963,12 +1076,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -976,7 +1089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -984,7 +1097,7 @@
         <v>45613</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -992,7 +1105,7 @@
         <v>0.71246527777777768</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1000,7 +1113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1008,7 +1121,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1016,13 +1129,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,12 +1143,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1043,16 +1156,16 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R17">
-        <f>(F25+G25)/2</f>
+        <f t="shared" ref="R17:R24" si="0">(F25+G25)/2</f>
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1060,11 +1173,11 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <f>(F26+G26)/2</f>
+        <f t="shared" si="0"/>
         <v>0.122</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1072,7 +1185,7 @@
         <v>4.5</v>
       </c>
       <c r="R19">
-        <f>(F27+G27)/2</f>
+        <f t="shared" si="0"/>
         <v>0.182</v>
       </c>
     </row>
@@ -1081,11 +1194,11 @@
         <v>4</v>
       </c>
       <c r="R20">
-        <f>(F28+G28)/2</f>
+        <f t="shared" si="0"/>
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1094,11 +1207,11 @@
         <v>3.5</v>
       </c>
       <c r="R21">
-        <f>(F29+G29)/2</f>
+        <f t="shared" si="0"/>
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -1109,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="R22">
-        <f>(F30+G30)/2</f>
+        <f t="shared" si="0"/>
         <v>0.249</v>
       </c>
     </row>
@@ -1118,7 +1231,7 @@
         <v>2.5</v>
       </c>
       <c r="R23">
-        <f>(F31+G31)/2</f>
+        <f t="shared" si="0"/>
         <v>0.32450000000000001</v>
       </c>
     </row>
@@ -1164,11 +1277,11 @@
         <v>2</v>
       </c>
       <c r="R24">
-        <f>(F32+G32)/2</f>
+        <f t="shared" si="0"/>
         <v>0.23250000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1219,7 +1332,7 @@
         <v>0.10300000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1266,11 +1379,11 @@
         <v>1</v>
       </c>
       <c r="R26">
-        <f t="shared" ref="R26:R32" si="0">(C26+D26)/2</f>
+        <f t="shared" ref="R26:R32" si="1">(C26+D26)/2</f>
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1317,11 +1430,11 @@
         <v>0.5</v>
       </c>
       <c r="R27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.9999999999999988E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1368,11 +1481,11 @@
         <v>0.25</v>
       </c>
       <c r="R28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1419,11 +1532,11 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="R29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1470,11 +1583,11 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="R30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7499999999999996E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1521,11 +1634,11 @@
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="R31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.5500000000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1572,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="R32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.2500000000000005E-2</v>
       </c>
     </row>
